--- a/data/trans_camb/IP1002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,55</t>
+          <t>-1,14; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,67</t>
+          <t>-2,99; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,99</t>
+          <t>-1,98; 5,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,65</t>
+          <t>-2,33; 3,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,26</t>
+          <t>-0,85; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; -0,58</t>
+          <t>-5,07; -0,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,17</t>
+          <t>-1,0; 3,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,01</t>
+          <t>-1,36; 2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,68</t>
+          <t>-2,71; 1,64</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 816,58</t>
+          <t>-72,93; 929,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 393,12</t>
+          <t>-69,16; 456,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 892,44</t>
+          <t>-41,16; 744,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 329,65</t>
+          <t>-35,28; 366,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 326,96</t>
+          <t>-50,41; 326,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,62</t>
+          <t>-100,0; 208,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,93</t>
+          <t>-1,85; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,19</t>
+          <t>-1,06; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,34</t>
+          <t>-0,85; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,82</t>
+          <t>0,4; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,38</t>
+          <t>-1,84; 1,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,84</t>
+          <t>-0,65; 5,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,94</t>
+          <t>-0,09; 2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,72</t>
+          <t>-0,94; 1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,75</t>
+          <t>-0,2; 3,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 320,27</t>
+          <t>-79,15; 304,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 458,43</t>
+          <t>-54,71; 442,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 609,86</t>
+          <t>-52,51; 760,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 1477,8</t>
+          <t>-7,15; 1101,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,87; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 1411,06</t>
+          <t>-70,75; 1053,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 361,54</t>
+          <t>-8,01; 344,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 208,15</t>
+          <t>-51,41; 209,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 444,08</t>
+          <t>-23,12; 382,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,51</t>
+          <t>-4,73; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,91</t>
+          <t>-5,66; -0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,46</t>
+          <t>-3,7; 1,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,81</t>
+          <t>-0,52; 3,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,45</t>
+          <t>-1,86; 1,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,6</t>
+          <t>-1,71; 1,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,65</t>
+          <t>-1,74; 1,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,11</t>
+          <t>-2,81; 0,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,92</t>
+          <t>-2,08; 1,03</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 251,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 198,63</t>
+          <t>-88,76; 240,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 306,53</t>
+          <t>-70,53; 254,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 62,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-83,44; 164,84</t>
+          <t>-83,66; 199,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,56</t>
+          <t>-0,64; 1,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,39</t>
+          <t>-0,64; 1,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,95</t>
+          <t>-1,97; 1,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,97</t>
+          <t>-1,98; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,0</t>
+          <t>-1,37; 2,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,9</t>
+          <t>-1,01; 0,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,73</t>
+          <t>-1,09; 0,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,02</t>
+          <t>-0,86; 1,03</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,64; 602,75</t>
+          <t>-83,42; 568,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,26</t>
+          <t>-1,0; 1,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-1,23; 0,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,05</t>
+          <t>-1,12; 0,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,33</t>
+          <t>0,22; 2,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,17</t>
+          <t>-0,73; 1,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,4</t>
+          <t>-0,78; 1,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,48</t>
+          <t>-0,03; 1,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,69</t>
+          <t>-0,73; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,83</t>
+          <t>-0,69; 0,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 143,43</t>
+          <t>-50,81; 117,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 89,53</t>
+          <t>-65,32; 77,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 121,12</t>
+          <t>-58,81; 93,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 333,44</t>
+          <t>4,84; 352,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 153,93</t>
+          <t>-46,48; 146,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 175,68</t>
+          <t>-51,33; 179,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 165,65</t>
+          <t>-5,32; 157,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 71,46</t>
+          <t>-44,43; 64,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 86,84</t>
+          <t>-42,23; 79,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,98</t>
+          <t>-0,87; 4,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,55</t>
+          <t>-2,74; 1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,93</t>
+          <t>-2,14; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,58</t>
+          <t>-2,84; 3,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,15</t>
+          <t>-1,33; 5,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,54</t>
+          <t>-5,15; -0,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,32</t>
+          <t>-1,02; 3,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,81</t>
+          <t>-1,27; 2,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,64</t>
+          <t>-2,58; 1,54</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 929,9</t>
+          <t>-55,34; 1113,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 456,12</t>
+          <t>-72,39; 407,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 744,38</t>
+          <t>-52,62; 683,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 366,91</t>
+          <t>-41,94; 350,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 326,91</t>
+          <t>-50,79; 297,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 208,12</t>
+          <t>-100,0; 262,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,77</t>
+          <t>-1,62; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,11</t>
+          <t>-1,03; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,25</t>
+          <t>-0,92; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,63</t>
+          <t>0,25; 4,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,21</t>
+          <t>-1,85; 1,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 5,12</t>
+          <t>-0,5; 5,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,67</t>
+          <t>-0,27; 2,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,59</t>
+          <t>-1,03; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,66</t>
+          <t>-0,16; 3,59</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,15; 304,03</t>
+          <t>-76,36; 318,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 442,44</t>
+          <t>-55,61; 476,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 760,69</t>
+          <t>-56,67; 547,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1101,07</t>
+          <t>-5,62; 1185,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,99; 455,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,75; 1053,12</t>
+          <t>-55,45; 1426,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 344,9</t>
+          <t>-19,55; 333,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 209,83</t>
+          <t>-52,96; 205,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 382,42</t>
+          <t>-23,2; 416,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,51</t>
+          <t>-4,98; 0,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,97</t>
+          <t>-6,12; -0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,53</t>
+          <t>-4,1; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,72</t>
+          <t>-0,49; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,38</t>
+          <t>-1,4; 1,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,56</t>
+          <t>-1,36; 1,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,66</t>
+          <t>-1,8; 1,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,04</t>
+          <t>-2,71; -0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,03</t>
+          <t>-1,96; 1,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 87,85</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 140,26</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-88,76; 240,12</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 254,55</t>
+          <t>-75,2; 249,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,63</t>
+          <t>-100,0; 32,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-83,66; 199,13</t>
+          <t>-80,66; 182,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,54</t>
+          <t>-0,64; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,46</t>
+          <t>-0,64; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,42; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,26</t>
+          <t>-1,77; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,88</t>
+          <t>-1,99; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,13</t>
+          <t>-1,48; 2,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,93</t>
+          <t>-1,14; 0,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,8</t>
+          <t>-1,09; 0,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,03</t>
+          <t>-0,82; 1,16</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 568,15</t>
+          <t>-87,03; 667,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,14</t>
+          <t>-0,81; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,64</t>
+          <t>-1,22; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,92</t>
+          <t>-1,1; 1,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,51</t>
+          <t>0,08; 2,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,07</t>
+          <t>-0,79; 1,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,37</t>
+          <t>-0,77; 1,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,51</t>
+          <t>-0,09; 1,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,62</t>
+          <t>-0,75; 0,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,76</t>
+          <t>-0,7; 0,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 117,38</t>
+          <t>-44,54; 139,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 77,94</t>
+          <t>-64,16; 73,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 93,71</t>
+          <t>-56,9; 118,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,84; 352,55</t>
+          <t>-3,91; 321,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 146,55</t>
+          <t>-49,93; 136,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 179,78</t>
+          <t>-51,55; 205,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 157,97</t>
+          <t>-7,22; 143,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 64,01</t>
+          <t>-44,36; 59,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 79,44</t>
+          <t>-44,86; 85,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,92</t>
+          <t>-2,42; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,64</t>
+          <t>-1,33; 6,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 5,61</t>
+          <t>-5,52; -0,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,61</t>
+          <t>-1,15; 4,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,51</t>
+          <t>-2,94; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -0,54</t>
+          <t>-2,08; 6,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,34</t>
+          <t>-1,14; 3,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,92</t>
+          <t>-1,25; 3,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,54</t>
+          <t>-2,45; 2,3</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>114,52%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-23,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-41,4%</t>
+          <t>-33,36%</t>
         </is>
       </c>
     </row>
@@ -783,29 +783,29 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 1113,13</t>
+          <t>-74,79; 393,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-51,82; 892,44</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-56,81; 816,58</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-72,39; 407,47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,62; 683,18</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,94; 350,45</t>
+          <t>-41,21; 329,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 297,43</t>
+          <t>-48,89; 326,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 262,15</t>
+          <t>-100,0; 363,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,04</t>
+          <t>0,26; 4,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,25</t>
+          <t>-1,7; 1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,29</t>
+          <t>-0,83; 4,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,71</t>
+          <t>-1,71; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,24</t>
+          <t>-1,01; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,3</t>
+          <t>-0,63; 4,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,75</t>
+          <t>-0,08; 2,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,6</t>
+          <t>-0,89; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,59</t>
+          <t>-0,16; 3,52</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>200,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-14,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>61,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>200,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-14,19%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>129,06%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101,32%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 318,6</t>
+          <t>-10,11; 1477,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 476,5</t>
+          <t>-84,87; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 547,26</t>
+          <t>-60,92; 1268,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1185,71</t>
+          <t>-74,56; 320,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,99; 455,92</t>
+          <t>-51,18; 458,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 1426,47</t>
+          <t>-38,85; 648,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 333,93</t>
+          <t>-17,93; 361,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 205,39</t>
+          <t>-48,85; 208,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 416,09</t>
+          <t>-13,93; 461,07</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,23</t>
+          <t>-0,34; 3,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -0,9</t>
+          <t>-1,52; 1,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,38</t>
+          <t>-1,5; 1,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,71</t>
+          <t>-4,77; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,53</t>
+          <t>-5,55; -0,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,63</t>
+          <t>-3,95; 1,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,51</t>
+          <t>-1,71; 1,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,07</t>
+          <t>-2,86; -0,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,02</t>
+          <t>-2,02; 1,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>263,32%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-64,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-37,38%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>263,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,8%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>-34,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,79%</t>
+          <t>-19,6%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 251,42</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-89,83; 222,76</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-74,2; 306,53</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-75,2; 249,9</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 32,62</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 182,48</t>
+          <t>-82,25; 183,66</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>-0,2</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,37</t>
+          <t>-1,98; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,75</t>
+          <t>-1,99; 0,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,0</t>
+          <t>-1,08; 2,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,27</t>
+          <t>-0,64; 1,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,88</t>
+          <t>-0,64; 1,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,2</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,75</t>
+          <t>-0,99; 0,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,64</t>
+          <t>-0,99; 0,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,16</t>
+          <t>-0,89; 1,19</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-45,64%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-55,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>47,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,29%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>40,21%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-45,64%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-55,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-29,92%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 667,57</t>
+          <t>-87,82; 659,67</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,22</t>
+          <t>0,04; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,68</t>
+          <t>-0,75; 1,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,0</t>
+          <t>-0,81; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,42</t>
+          <t>-0,87; 1,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,03</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,46</t>
+          <t>-1,06; 1,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,44</t>
+          <t>-0,06; 1,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,57</t>
+          <t>-0,75; 0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,84</t>
+          <t>-0,66; 0,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>102,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-22,18%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>-2,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 139,71</t>
+          <t>-3,22; 333,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 73,01</t>
+          <t>-46,01; 153,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 118,48</t>
+          <t>-51,11; 176,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 321,08</t>
+          <t>-47,55; 143,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 136,18</t>
+          <t>-64,08; 89,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 205,32</t>
+          <t>-58,94; 130,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 143,26</t>
+          <t>-5,73; 165,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 59,28</t>
+          <t>-43,99; 71,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 85,7</t>
+          <t>-40,78; 91,79</t>
         </is>
       </c>
     </row>
